--- a/data/trans_dic/IP11C$ingresado-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,87</t>
+          <t>0,0; 63,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,67</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,49 +737,49 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,55</t>
+          <t>0,0; 50,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,08</t>
+          <t>0,0; 59,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,13</t>
+          <t>0,0; 33,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,09</t>
+          <t>0,0; 64,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,54</t>
+          <t>0,0; 52,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,51</t>
+          <t>0,0; 51,98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,31</t>
+          <t>0,0; 42,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,68</t>
+          <t>0,0; 19,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,14</t>
+          <t>0,0; 63,26</t>
         </is>
       </c>
     </row>
@@ -1136,37 +1137,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,88</t>
+          <t>0,0; 60,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,12</t>
+          <t>0,0; 50,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,71</t>
+          <t>0,0; 87,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1176,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,25</t>
+          <t>0,0; 31,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,61</t>
+          <t>0,0; 69,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,54</t>
+          <t>0,0; 26,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1306,39 +1307,39 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,06</t>
+          <t>0,0; 66,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,75</t>
+          <t>0,0; 38,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,05</t>
+          <t>0,0; 16,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,81</t>
+          <t>0,0; 51,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,27</t>
+          <t>0,0; 22,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,14</t>
+          <t>0,0; 20,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,66</t>
+          <t>0,0; 51,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,56</t>
+          <t>0,0; 20,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,31</t>
+          <t>0,0; 12,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,64</t>
+          <t>0,0; 30,73</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,74</t>
+          <t>0,0; 44,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,82</t>
+          <t>0,0; 66,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,58</t>
+          <t>0,0; 30,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,26</t>
+          <t>0,0; 65,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,7</t>
+          <t>0,0; 36,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,76</t>
+          <t>0,0; 18,72</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,54</t>
+          <t>0,0; 34,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,0</t>
+          <t>0,0; 34,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,51</t>
+          <t>2,15; 12,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 20,42</t>
+          <t>2,0; 20,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 26,27</t>
+          <t>2,48; 29,19</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,22</t>
+          <t>1,78; 12,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,85; 15,19</t>
+          <t>3,57; 14,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,42</t>
+          <t>0,0; 14,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 14,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,48</t>
+          <t>1,33; 8,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,77; 11,87</t>
+          <t>3,88; 11,79</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 12,43</t>
+          <t>1,89; 12,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 15,48</t>
+          <t>2,72; 15,29</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria e ingresaron en un hospital o clínica (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2902</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2410</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2596</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3675</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4094</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3626</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4502</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3612</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4083</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3960</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1875</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2430</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2256</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>530</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2983</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4021</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4030</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2046</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4694</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5060</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3363</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2992</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1975</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2693</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3015</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3534</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2063</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2648</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4187</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3545</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3794</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4065</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3331</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>1105</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2507</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2067</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2587</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2660</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2653</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2511</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3372</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3613</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1741</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>3294</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>8782</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>0; 4102</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6493</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>466; 4782</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>426; 5006</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>828; 5819</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2622; 10939</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>0; 6094</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3587</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1090; 6957</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>4854; 14751</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>1208; 7742</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1118; 6299</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$ingresado-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Provincia-trans_dic.xlsx
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,14</t>
+          <t>0,0; 62,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,61</t>
+          <t>0,0; 61,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,74</t>
+          <t>0,0; 32,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,09</t>
+          <t>0,0; 62,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,69</t>
+          <t>0,0; 59,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,98</t>
+          <t>0,0; 54,51</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,28</t>
+          <t>0,0; 42,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,94</t>
+          <t>0,0; 20,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,26</t>
+          <t>0,0; 68,18</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,31</t>
+          <t>0,0; 59,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,28</t>
+          <t>0,0; 50,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,74</t>
+          <t>0,0; 87,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,65</t>
+          <t>0,0; 28,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,15</t>
+          <t>0,0; 67,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,32</t>
+          <t>0,0; 27,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,29</t>
+          <t>0,0; 67,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,27</t>
+          <t>0,0; 40,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,8</t>
+          <t>0,0; 18,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,53</t>
+          <t>0,0; 54,07</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,66</t>
+          <t>0,0; 23,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,45</t>
+          <t>0,0; 21,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,85</t>
+          <t>0,0; 42,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,48</t>
+          <t>0,0; 19,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 12,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,73</t>
+          <t>0,0; 31,83</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,72</t>
+          <t>0,0; 44,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,28</t>
+          <t>0,0; 65,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,31</t>
+          <t>0,0; 25,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,27</t>
+          <t>0,0; 66,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,62</t>
+          <t>0,0; 36,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,72</t>
+          <t>0,0; 21,83</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,84</t>
+          <t>0,0; 35,93</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,87</t>
+          <t>0,0; 32,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 11,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,56</t>
+          <t>2,13; 12,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 20,46</t>
+          <t>2,03; 19,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 29,19</t>
+          <t>2,32; 26,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,51</t>
+          <t>1,4; 12,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,57; 14,91</t>
+          <t>3,58; 15,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 14,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,93</t>
+          <t>0,0; 15,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,5</t>
+          <t>1,47; 8,72</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,79</t>
+          <t>3,98; 11,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,08</t>
+          <t>1,79; 12,64</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,29</t>
+          <t>2,8; 16,65</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2596</t>
+          <t>0; 3230</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3675</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4094</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3626</t>
+          <t>0; 3524</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4502</t>
+          <t>0; 5091</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3788</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4083</t>
+          <t>0; 4078</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3960</t>
+          <t>0; 4050</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2430</t>
+          <t>0; 2619</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2983</t>
+          <t>0; 2945</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4021</t>
+          <t>0; 4011</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4030</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4694</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5060</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>0; 3498</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2693</t>
+          <t>0; 2734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3015</t>
+          <t>0; 3194</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3534</t>
+          <t>0; 3968</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2063</t>
+          <t>0; 2164</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2648</t>
+          <t>0; 2707</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4187</t>
+          <t>0; 4409</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3545</t>
+          <t>0; 2884</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3794</t>
+          <t>0; 3655</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4065</t>
+          <t>0; 4200</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 3331</t>
+          <t>0; 3450</t>
         </is>
       </c>
     </row>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2507</t>
+          <t>0; 2502</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>0; 2035</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 2587</t>
+          <t>0; 2176</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2660</t>
+          <t>0; 2708</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2653</t>
+          <t>0; 2621</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 2511</t>
+          <t>0; 2927</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 3372</t>
+          <t>0; 3478</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 3613</t>
+          <t>0; 3357</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4102</t>
+          <t>0; 3891</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1113; 6493</t>
+          <t>1104; 6523</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>466; 4782</t>
+          <t>475; 4666</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>426; 5006</t>
+          <t>398; 4493</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>828; 5819</t>
+          <t>649; 6043</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2622; 10939</t>
+          <t>2626; 11425</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 6094</t>
+          <t>0; 5980</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 3587</t>
+          <t>0; 3831</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1090; 6957</t>
+          <t>1203; 7132</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4854; 14751</t>
+          <t>4976; 14887</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1208; 7742</t>
+          <t>1150; 8103</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1118; 6299</t>
+          <t>1151; 6858</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$ingresado-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$ingresado-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>16,03%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>25,93%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 61,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 61,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 60,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,18</t>
+          <t>0,0; 78,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 75,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,51</t>
+          <t>0,0; 30,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,29</t>
+          <t>0,0; 63,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,58</t>
+          <t>0,0; 54,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,51</t>
+          <t>0,0; 51,47</t>
         </is>
       </c>
     </row>
@@ -794,27 +794,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>13,48%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,39</t>
+          <t>0,0; 19,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1012,29 +1012,29 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,18</t>
+          <t>0,0; 75,62</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22,89%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
           <t>13,03%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -1137,57 +1137,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 54,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 87,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 87,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 61,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,5</t>
+          <t>0,0; 30,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,88</t>
+          <t>0,0; 70,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,37</t>
+          <t>0,0; 27,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,12 +1209,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1224,27 +1224,27 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>34,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,3</t>
+          <t>0,0; 67,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1354,27 +1354,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>8,91%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 52,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,87</t>
+          <t>0,0; 17,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1504,17 +1504,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1524,27 +1524,27 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>9,34%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>9,21%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,17 +1572,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,07</t>
+          <t>0,0; 47,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,18</t>
+          <t>0,0; 48,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,73</t>
+          <t>0,0; 15,56</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,95</t>
+          <t>0,0; 14,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,83</t>
+          <t>0,0; 30,76</t>
         </is>
       </c>
     </row>
@@ -1629,37 +1629,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8,64%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>10,86%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>15,36%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,64</t>
+          <t>0,0; 66,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,26</t>
+          <t>0,0; 36,7</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,17 +1717,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,45</t>
+          <t>0,0; 44,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,19</t>
+          <t>0,0; 64,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,83</t>
+          <t>0,0; 19,76</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,93</t>
+          <t>0,0; 40,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,39</t>
+          <t>0,0; 30,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,5%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2,09%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5,98%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>7,45%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,02</t>
+          <t>1,29; 13,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,61</t>
+          <t>2,85; 15,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,97</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,32; 26,2</t>
+          <t>0,0; 15,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,99</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,58; 15,57</t>
+          <t>1,29; 11,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>2,01; 20,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,94</t>
+          <t>2,09; 25,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,72</t>
+          <t>1,47; 8,48</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,9</t>
+          <t>3,77; 11,87</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 12,64</t>
+          <t>1,76; 12,43</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,65</t>
+          <t>2,2; 15,23</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>779</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>667</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2902</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3187</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2380</t>
+          <t>0; 3766</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2410</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2799</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3230</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3772</t>
+          <t>0; 1872</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2258</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 3524</t>
+          <t>0; 3570</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5091</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3788</t>
+          <t>0; 3078</t>
         </is>
       </c>
     </row>
@@ -2286,27 +2286,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1302</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4078</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3603</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 3909</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2504,27 +2504,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>592</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>592</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1760</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 2591</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,54 +2765,54 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>645</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1425</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>2256</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2256</t>
-        </is>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
           <t>644</t>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>453</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1979</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4028</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3061</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4226</t>
+          <t>0; 4485</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4967</t>
+          <t>0; 5168</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 3498</t>
+          <t>0; 3519</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 2992</t>
+          <t>0; 3030</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>675</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2988,27 +2988,27 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1975</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 1975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2734</t>
+          <t>0; 2725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3118,27 +3118,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -3186,27 +3186,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>702</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3194</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4155</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3968</t>
+          <t>0; 3585</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3404,39 +3404,39 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>626</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>644</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>1300</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>992</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4327</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 2164</t>
+          <t>0; 3237</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2707</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4409</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,17 +3492,17 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2884</t>
+          <t>0; 1891</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 2882</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4200</t>
+          <t>0; 4642</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 3450</t>
+          <t>0; 3315</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3597,37 +3597,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>488</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>479</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2525</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2502</t>
+          <t>0; 2700</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2035</t>
+          <t>0; 2659</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,17 +3685,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 2176</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2708</t>
+          <t>0; 2508</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 2621</t>
+          <t>0; 2021</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3705,17 +3705,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 2927</t>
+          <t>0; 2650</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 3478</t>
+          <t>0; 3924</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 3357</t>
+          <t>0; 3109</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>1673</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>3093</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>1740</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1741</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2557</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>1673</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2705</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 3891</t>
+          <t>599; 6149</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1104; 6523</t>
+          <t>2089; 11146</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>475; 4666</t>
+          <t>0; 5466</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>398; 4493</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>649; 6043</t>
+          <t>0; 4416</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2626; 11425</t>
+          <t>669; 5952</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0; 5980</t>
+          <t>471; 4772</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>0; 3831</t>
+          <t>359; 4385</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1203; 7132</t>
+          <t>1204; 6940</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4976; 14887</t>
+          <t>4717; 14850</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1150; 8103</t>
+          <t>1126; 7966</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1151; 6858</t>
+          <t>869; 6005</t>
         </is>
       </c>
     </row>
